--- a/no_match_residual/no_match_residual_2023.xlsx
+++ b/no_match_residual/no_match_residual_2023.xlsx
@@ -583,21 +583,21 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -666,21 +666,21 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -749,21 +749,21 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -832,21 +832,21 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -1247,21 +1247,21 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1330,21 +1330,21 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -1413,21 +1413,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -1496,21 +1496,21 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1579,21 +1579,21 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -1662,21 +1662,21 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -1745,21 +1745,21 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -1828,21 +1828,21 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1911,21 +1911,21 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1994,21 +1994,21 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -2077,21 +2077,21 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -2160,21 +2160,21 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -3559,21 +3559,21 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -3642,21 +3642,21 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -3725,21 +3725,21 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -3808,21 +3808,21 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -3891,21 +3891,21 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -3974,21 +3974,21 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -4057,21 +4057,21 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4140,21 +4140,21 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -4221,21 +4221,21 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -4302,21 +4302,21 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -4383,21 +4383,21 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -4464,21 +4464,21 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -4547,21 +4547,21 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -4628,21 +4628,21 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -4709,21 +4709,21 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -4790,21 +4790,21 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -4871,21 +4871,21 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S54" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -4952,21 +4952,21 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
@@ -5033,21 +5033,21 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -5116,21 +5116,21 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -5197,21 +5197,21 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -5278,21 +5278,21 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S59" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -5359,21 +5359,21 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -5440,21 +5440,21 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -5521,21 +5521,21 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -5602,21 +5602,21 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -6483,21 +6483,21 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -6566,21 +6566,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -6815,21 +6815,21 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -6898,21 +6898,21 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -16611,21 +16611,21 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S196" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197">
@@ -16696,21 +16696,21 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198">
@@ -17443,21 +17443,21 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S206" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207">
@@ -17526,21 +17526,21 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S207" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208">
@@ -17775,21 +17775,21 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Herramientas/Equipamiento</t>
         </is>
       </c>
       <c r="S210" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211">
@@ -17858,21 +17858,21 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Herramientas/Equipamiento</t>
         </is>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="212">
@@ -17941,21 +17941,21 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Herramientas/Equipamiento</t>
         </is>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="213">
@@ -18024,21 +18024,21 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>80000000</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Herramientas/Equipamiento</t>
         </is>
       </c>
       <c r="S213" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="214">
@@ -19727,21 +19727,21 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S234" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235">
@@ -19802,21 +19802,21 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S235" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="236">
@@ -20201,21 +20201,21 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S240" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241">
@@ -20276,21 +20276,21 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S241" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="242">
@@ -20683,21 +20683,21 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247">
@@ -20766,21 +20766,21 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -20849,21 +20849,21 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="249">
@@ -20932,21 +20932,21 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S249" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250">
@@ -21015,21 +21015,21 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S250" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251">
@@ -21098,21 +21098,21 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252">
@@ -21181,21 +21181,21 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S252" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253">
@@ -21264,21 +21264,21 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S253" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254">
@@ -21347,21 +21347,21 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S254" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="255">
@@ -21430,21 +21430,21 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S255" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="256">
@@ -21513,21 +21513,21 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S256" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257">
@@ -21596,21 +21596,21 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S257" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="258">
@@ -21679,21 +21679,21 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259">
@@ -21762,21 +21762,21 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S259" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260">
@@ -21845,21 +21845,21 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261">
@@ -21928,21 +21928,21 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262">
@@ -22011,21 +22011,21 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S262" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263">
@@ -22094,21 +22094,21 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S263" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="264">
@@ -22177,21 +22177,21 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S264" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265">
@@ -22260,21 +22260,21 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S265" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266">
@@ -22343,21 +22343,21 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S266" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267">
@@ -22426,21 +22426,21 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S267" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268">
@@ -22509,21 +22509,21 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S268" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269">
@@ -22592,21 +22592,21 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="270">
@@ -22675,21 +22675,21 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S270" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="271">
@@ -22758,21 +22758,21 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S271" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="272">
@@ -22841,21 +22841,21 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S272" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="273">
@@ -22924,21 +22924,21 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S273" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274">
@@ -23007,21 +23007,21 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S274" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="275">
@@ -23090,21 +23090,21 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S275" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="276">
@@ -23173,21 +23173,21 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S276" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="277">
@@ -23256,21 +23256,21 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S277" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="278">
@@ -23339,21 +23339,21 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S278" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="279">
@@ -23422,21 +23422,21 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S279" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="280">
@@ -23505,21 +23505,21 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S280" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="281">
@@ -23588,21 +23588,21 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="282">
@@ -23671,21 +23671,21 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S282" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="283">
@@ -23754,21 +23754,21 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S283" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284">
@@ -23837,21 +23837,21 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S284" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="285">
@@ -23920,21 +23920,21 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S285" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286">
@@ -24001,21 +24001,21 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S286" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287">
@@ -24082,21 +24082,21 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S287" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="288">
@@ -24163,21 +24163,21 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S288" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="289">
@@ -24244,21 +24244,21 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S289" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="290">
@@ -24319,21 +24319,21 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S290" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="291">
@@ -24544,21 +24544,21 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S293" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="294">
@@ -25275,21 +25275,21 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S302" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303">
@@ -25358,21 +25358,21 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S303" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="304">
@@ -25441,21 +25441,21 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S304" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="305">
@@ -25690,21 +25690,21 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S307" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308">
@@ -25773,21 +25773,21 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S308" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="309">
@@ -25856,21 +25856,21 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S309" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310">
@@ -25939,21 +25939,21 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S310" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="311">
@@ -26022,21 +26022,21 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S311" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312">
@@ -26105,21 +26105,21 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S312" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="313">
@@ -26188,21 +26188,21 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S313" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314">
@@ -26271,21 +26271,21 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S314" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315">
@@ -26354,21 +26354,21 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S315" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="316">
@@ -26437,21 +26437,21 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S316" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="317">
@@ -26520,21 +26520,21 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S317" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="318">
@@ -26935,21 +26935,21 @@
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S322" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="323">
@@ -27350,21 +27350,21 @@
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S327" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="328">
@@ -27915,21 +27915,21 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S334" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="335">
@@ -27998,21 +27998,21 @@
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S335" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="336">
@@ -28079,21 +28079,21 @@
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S336" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="337">
@@ -28162,21 +28162,21 @@
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S337" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="338">
@@ -28243,21 +28243,21 @@
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S338" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="339">
@@ -28326,21 +28326,21 @@
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S339" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="340">
@@ -28407,21 +28407,21 @@
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S340" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="341">
@@ -28488,21 +28488,21 @@
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S341" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="342">
@@ -28569,21 +28569,21 @@
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S342" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="343">
@@ -28650,21 +28650,21 @@
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S343" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="344">
@@ -28731,21 +28731,21 @@
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S344" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="345">
@@ -28812,21 +28812,21 @@
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S345" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="346">
@@ -28895,21 +28895,21 @@
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S346" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="347">
@@ -28978,21 +28978,21 @@
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S347" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="348">
@@ -29061,21 +29061,21 @@
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S348" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="349">
@@ -29144,21 +29144,21 @@
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S349" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="350">
@@ -29225,21 +29225,21 @@
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S350" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="351">
@@ -29306,21 +29306,21 @@
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S351" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="352">
@@ -29387,21 +29387,21 @@
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S352" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="353">
@@ -29468,21 +29468,21 @@
       </c>
       <c r="P353" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S353" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="354">
@@ -29549,21 +29549,21 @@
       </c>
       <c r="P354" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S354" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="355">
@@ -29630,21 +29630,21 @@
       </c>
       <c r="P355" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S355" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356">
@@ -29711,21 +29711,21 @@
       </c>
       <c r="P356" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S356" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="357">
@@ -29792,21 +29792,21 @@
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S357" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="358">
@@ -29873,21 +29873,21 @@
       </c>
       <c r="P358" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q358" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S358" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="359">
@@ -29954,21 +29954,21 @@
       </c>
       <c r="P359" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S359" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="360">
@@ -30035,21 +30035,21 @@
       </c>
       <c r="P360" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S360" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="361">
@@ -30116,21 +30116,21 @@
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S361" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="362">
@@ -30197,21 +30197,21 @@
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S362" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="363">
@@ -30278,21 +30278,21 @@
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S363" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="364">
@@ -30361,21 +30361,21 @@
       </c>
       <c r="P364" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S364" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="365">
@@ -30442,21 +30442,21 @@
       </c>
       <c r="P365" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S365" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="366">
@@ -30525,21 +30525,21 @@
       </c>
       <c r="P366" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S366" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="367">
@@ -30606,21 +30606,21 @@
       </c>
       <c r="P367" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S367" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="368">
@@ -30687,21 +30687,21 @@
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S368" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="369">
@@ -30768,21 +30768,21 @@
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S369" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="370">
@@ -30849,21 +30849,21 @@
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S370" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="371">
@@ -30930,21 +30930,21 @@
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S371" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="372">
@@ -31011,21 +31011,21 @@
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S372" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="373">
@@ -31094,21 +31094,21 @@
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S373" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="374">
@@ -31177,21 +31177,21 @@
       </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S374" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="375">
@@ -31260,21 +31260,21 @@
       </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S375" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="376">
@@ -31343,21 +31343,21 @@
       </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S376" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="377">
@@ -31424,21 +31424,21 @@
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S377" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="378">
@@ -31505,21 +31505,21 @@
       </c>
       <c r="P378" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S378" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="379">
@@ -31586,21 +31586,21 @@
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S379" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="380">
@@ -31667,21 +31667,21 @@
       </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q380" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S380" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="381">
@@ -31748,21 +31748,21 @@
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S381" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="382">
@@ -31829,21 +31829,21 @@
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S382" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="383">
@@ -31910,21 +31910,21 @@
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S383" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384">
@@ -31991,21 +31991,21 @@
       </c>
       <c r="P384" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S384" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385">
@@ -32072,21 +32072,21 @@
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S385" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="386">
@@ -32153,21 +32153,21 @@
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S386" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="387">
@@ -32234,21 +32234,21 @@
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S387" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388">
@@ -32315,21 +32315,21 @@
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S388" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="389">
@@ -32396,21 +32396,21 @@
       </c>
       <c r="P389" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q389" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S389" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="390">
@@ -32645,21 +32645,21 @@
       </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S392" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="393">
@@ -32728,21 +32728,21 @@
       </c>
       <c r="P393" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S393" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="394">
@@ -32811,21 +32811,21 @@
       </c>
       <c r="P394" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S394" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="395">
@@ -32894,21 +32894,21 @@
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S395" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="396">
@@ -32977,21 +32977,21 @@
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S396" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="397">
@@ -33060,21 +33060,21 @@
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S397" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="398">
@@ -33467,21 +33467,21 @@
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S402" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="403">
@@ -33552,21 +33552,21 @@
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S403" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="404">
@@ -33635,21 +33635,21 @@
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S404" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="405">
@@ -33720,21 +33720,21 @@
       </c>
       <c r="P405" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S405" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="406">
@@ -33803,21 +33803,21 @@
       </c>
       <c r="P406" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S406" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="407">
@@ -33886,21 +33886,21 @@
       </c>
       <c r="P407" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S407" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="408">
@@ -33969,21 +33969,21 @@
       </c>
       <c r="P408" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S408" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="409">
@@ -34052,21 +34052,21 @@
       </c>
       <c r="P409" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S409" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="410">
@@ -34135,21 +34135,21 @@
       </c>
       <c r="P410" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q410" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S410" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="411">
@@ -34218,21 +34218,21 @@
       </c>
       <c r="P411" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S411" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="412">
@@ -34301,21 +34301,21 @@
       </c>
       <c r="P412" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S412" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="413">
@@ -34384,21 +34384,21 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S413" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="414">
@@ -34467,21 +34467,21 @@
       </c>
       <c r="P414" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S414" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="415">
@@ -34550,21 +34550,21 @@
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S415" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="416">
@@ -34633,21 +34633,21 @@
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="417">
@@ -34716,21 +34716,21 @@
       </c>
       <c r="P417" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S417" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="418">
@@ -34799,21 +34799,21 @@
       </c>
       <c r="P418" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R418" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S418" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="419">
@@ -34882,21 +34882,21 @@
       </c>
       <c r="P419" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q419" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R419" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S419" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="420">
@@ -34965,21 +34965,21 @@
       </c>
       <c r="P420" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q420" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R420" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S420" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="421">
@@ -35048,21 +35048,21 @@
       </c>
       <c r="P421" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q421" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R421" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S421" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="422">
@@ -35131,21 +35131,21 @@
       </c>
       <c r="P422" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q422" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R422" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S422" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="423">
@@ -35214,21 +35214,21 @@
       </c>
       <c r="P423" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R423" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S423" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="424">
@@ -35297,21 +35297,21 @@
       </c>
       <c r="P424" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R424" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S424" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="425">
@@ -35380,21 +35380,21 @@
       </c>
       <c r="P425" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R425" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S425" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="426">
@@ -35463,21 +35463,21 @@
       </c>
       <c r="P426" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R426" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S426" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="427">
@@ -35546,21 +35546,21 @@
       </c>
       <c r="P427" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R427" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S427" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="428">
@@ -35629,21 +35629,21 @@
       </c>
       <c r="P428" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R428" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S428" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="429">
@@ -35710,21 +35710,21 @@
       </c>
       <c r="P429" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R429" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S429" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="430">
@@ -35791,21 +35791,21 @@
       </c>
       <c r="P430" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R430" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S430" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="431">
@@ -35872,21 +35872,21 @@
       </c>
       <c r="P431" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S431" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="432">
@@ -35953,21 +35953,21 @@
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S432" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="433">
@@ -36034,21 +36034,21 @@
       </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S433" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="434">
@@ -36115,21 +36115,21 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S434" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="435">
@@ -36196,21 +36196,21 @@
       </c>
       <c r="P435" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R435" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S435" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="436">
@@ -36277,21 +36277,21 @@
       </c>
       <c r="P436" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S436" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="437">
@@ -36358,21 +36358,21 @@
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q437" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S437" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="438">
@@ -36441,21 +36441,21 @@
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S438" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="439">
@@ -36522,21 +36522,21 @@
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S439" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="440">
@@ -36603,21 +36603,21 @@
       </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S440" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="441">
@@ -36684,21 +36684,21 @@
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S441" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="442">
@@ -36765,21 +36765,21 @@
       </c>
       <c r="P442" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S442" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="443">
@@ -36846,21 +36846,21 @@
       </c>
       <c r="P443" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S443" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="444">
@@ -36927,21 +36927,21 @@
       </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S444" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="445">
@@ -37008,21 +37008,21 @@
       </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S445" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="446">
@@ -37089,21 +37089,21 @@
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S446" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="447">
@@ -37170,21 +37170,21 @@
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S447" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="448">
@@ -37253,21 +37253,21 @@
       </c>
       <c r="P448" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S448" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="449">
@@ -37336,21 +37336,21 @@
       </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S449" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="450">
@@ -37419,21 +37419,21 @@
       </c>
       <c r="P450" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S450" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="451">
@@ -37502,21 +37502,21 @@
       </c>
       <c r="P451" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q451" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S451" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="452">
@@ -37585,21 +37585,21 @@
       </c>
       <c r="P452" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q452" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S452" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="453">
@@ -37668,21 +37668,21 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S453" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="454">
@@ -37751,21 +37751,21 @@
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S454" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="455">
@@ -37834,21 +37834,21 @@
       </c>
       <c r="P455" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q455" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S455" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="456">
@@ -37917,21 +37917,21 @@
       </c>
       <c r="P456" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q456" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S456" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="457">
@@ -38000,21 +38000,21 @@
       </c>
       <c r="P457" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S457" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="458">
@@ -38083,21 +38083,21 @@
       </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q458" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S458" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="459">
@@ -38166,21 +38166,21 @@
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S459" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="460">
@@ -38249,21 +38249,21 @@
       </c>
       <c r="P460" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q460" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S460" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="461">
@@ -38332,21 +38332,21 @@
       </c>
       <c r="P461" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q461" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S461" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="462">
@@ -38415,21 +38415,21 @@
       </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q462" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S462" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="463">
@@ -38498,21 +38498,21 @@
       </c>
       <c r="P463" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q463" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S463" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="464">
@@ -38583,21 +38583,21 @@
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q464" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S464" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="465">
@@ -38668,21 +38668,21 @@
       </c>
       <c r="P465" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S465" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="466">
@@ -38753,21 +38753,21 @@
       </c>
       <c r="P466" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S466" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="467">
@@ -38838,21 +38838,21 @@
       </c>
       <c r="P467" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q467" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S467" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="468">
@@ -38923,21 +38923,21 @@
       </c>
       <c r="P468" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q468" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S468" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="469">
@@ -39008,21 +39008,21 @@
       </c>
       <c r="P469" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S469" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="470">
@@ -39093,21 +39093,21 @@
       </c>
       <c r="P470" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S470" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="471">
@@ -39178,21 +39178,21 @@
       </c>
       <c r="P471" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S471" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="472">
@@ -39261,21 +39261,21 @@
       </c>
       <c r="P472" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S472" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="473">
@@ -39344,21 +39344,21 @@
       </c>
       <c r="P473" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S473" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="474">
@@ -39423,21 +39423,21 @@
       </c>
       <c r="P474" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S474" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
